--- a/Sedes_a_priorizar_Nasa_CxaCxa.xlsx
+++ b/Sedes_a_priorizar_Nasa_CxaCxa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,14 +450,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="B2" t="n">
-        <v>219517001670</v>
+        <v>219517800017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA TIERRAS BLANCAS</t>
+          <t>ESCUELA RURAL MIXTA PIYA YAT EL CHUMAL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -467,7 +467,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LAME</t>
+          <t>TOGOIMA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -476,19 +476,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>47.04318137931034</v>
+        <v>46.10072775862069</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>340</v>
+        <v>391</v>
       </c>
       <c r="B3" t="n">
-        <v>219517000169</v>
+        <v>219517001670</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ESCUELA EL CARMEN DEL SALADO</t>
+          <t>ESCUELA RURAL MIXTA TIERRAS BLANCAS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BELALCAZAR</t>
+          <t>LAME</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -507,37 +507,99 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>51.66638465517241</v>
+        <v>47.04318137931034</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>645</v>
+      </c>
+      <c r="B4" t="n">
+        <v>219517000452</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ESCUELA RURAL MIXTA SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TIERRA DENTRO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MOSOCO</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PAEZ</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48.81196051724138</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>340</v>
+      </c>
+      <c r="B5" t="n">
+        <v>219517000169</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ESCUELA EL CARMEN DEL SALADO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TIERRA DENTRO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BELALCAZAR</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PAEZ</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>51.66638465517241</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>348</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>219517000428</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>CENTRO DOCENTE LA HONDA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TIERRA DENTRO</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>RICAURTE</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>PAEZ</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="G6" t="n">
         <v>53.88823827586207</v>
       </c>
     </row>

--- a/Sedes_a_priorizar_Nasa_CxaCxa.xlsx
+++ b/Sedes_a_priorizar_Nasa_CxaCxa.xlsx
@@ -450,7 +450,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B2" t="n">
         <v>219517800017</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B3" t="n">
         <v>219517001670</v>
@@ -512,7 +512,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B4" t="n">
         <v>219517000452</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B5" t="n">
         <v>219517000169</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B6" t="n">
         <v>219517000428</v>
